--- a/tables/ov_1_clean_test_anomaly_counts.xlsx
+++ b/tables/ov_1_clean_test_anomaly_counts.xlsx
@@ -419,22 +419,22 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>Methode</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Detected Anomalies</t>
+          <t>Anomalien erkannt</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Detected Normal</t>
+          <t>Normal erkannt</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Anomaly Rate</t>
+          <t>Anomalierate</t>
         </is>
       </c>
     </row>
